--- a/backend/temp_gb.xlsx
+++ b/backend/temp_gb.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +51,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,244 +430,851 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Student Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Quiz 1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quiz 2</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Final Exam</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Total Grade</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>course_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>logins</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>assignments</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>quizzes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>forum</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>study_hours</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>activities_completed</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>محمد علي</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>STU001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ahmed Ali</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>student1@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+966500000001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>85</v>
       </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>88</v>
-      </c>
-      <c r="E2" t="n">
-        <v>87</v>
-      </c>
-      <c r="F2" t="n">
-        <v>89</v>
-      </c>
       <c r="G2" t="n">
-        <v>87.8</v>
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" t="n">
+        <v>63</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>فاطمة أحمد</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>92</v>
-      </c>
-      <c r="C3" t="n">
-        <v>88</v>
-      </c>
-      <c r="D3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E3" t="n">
-        <v>91</v>
+          <t>STU002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sara Khaled</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>student2@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+966500000002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Odoo Enterprise</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>71</v>
+      </c>
+      <c r="H3" t="n">
+        <v>76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>57</v>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>علي محمود</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>78</v>
-      </c>
-      <c r="C4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E4" t="n">
-        <v>79</v>
+          <t>STU003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Omar Hussein</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>student3@example.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+966500000003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Odoo Enterprise</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>72</v>
+      </c>
+      <c r="K4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>نور السيد</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>88</v>
-      </c>
-      <c r="C5" t="n">
-        <v>85</v>
-      </c>
-      <c r="D5" t="n">
+          <t>STU004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Noura Saad</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>student4@example.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+966500000004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>142</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="n">
         <v>87</v>
       </c>
-      <c r="E5" t="n">
-        <v>86</v>
-      </c>
-      <c r="F5" t="n">
-        <v>88</v>
-      </c>
-      <c r="G5" t="n">
-        <v>86.8</v>
+      <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>هناء حسن</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>95</v>
-      </c>
-      <c r="C6" t="n">
-        <v>92</v>
-      </c>
-      <c r="D6" t="n">
-        <v>94</v>
-      </c>
-      <c r="E6" t="n">
-        <v>93</v>
+          <t>STU005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Khalid Mansour</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>student5@example.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+966500000005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Odoo Enterprise</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" t="n">
+        <v>64</v>
+      </c>
+      <c r="K6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>خالد عمر</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>72</v>
-      </c>
-      <c r="C7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D7" t="n">
-        <v>73</v>
-      </c>
-      <c r="E7" t="n">
-        <v>74</v>
+          <t>STU006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Salma Jaziri</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>student6@example.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+966500000006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>83</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>67</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>مريم صالح</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>89</v>
-      </c>
-      <c r="C8" t="n">
-        <v>87</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88</v>
-      </c>
-      <c r="E8" t="n">
-        <v>90</v>
+          <t>STU007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Karim Sassi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>student7@example.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+966500000007</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>89.2</v>
+        <v>92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>92</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>62</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>أحمد جمال</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>91</v>
-      </c>
-      <c r="C9" t="n">
-        <v>93</v>
-      </c>
-      <c r="D9" t="n">
-        <v>89</v>
-      </c>
-      <c r="E9" t="n">
-        <v>92</v>
+          <t>STU008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rania Noor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>student8@example.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+966500000008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>91.8</v>
+        <v>86</v>
+      </c>
+      <c r="H9" t="n">
+        <v>78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>78</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STU009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fahad Salem</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>student9@example.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+966500000009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G10" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23</v>
+      </c>
+      <c r="J10" t="n">
+        <v>53</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STU010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lina Youssef</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>student10@example.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+966500000010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>151</v>
+      </c>
+      <c r="G11" t="n">
+        <v>66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>63</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23</v>
+      </c>
+      <c r="J11" t="n">
+        <v>86</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STU011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mohammed Adel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>student11@example.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+966500000011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>121</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" t="n">
+        <v>72</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>64</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STU012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Huda Fares</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>student12@example.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>+966500000012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G13" t="n">
+        <v>64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STU013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yousef Sami</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>student13@example.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>+966500000013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Odoo Enterprise</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>131</v>
+      </c>
+      <c r="G14" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>86</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STU014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Maha Essam</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>student14@example.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>+966500000014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>47</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" t="n">
+        <v>51</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STU015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ziad Tarek</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>student15@example.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>+966500000015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>90</v>
+      </c>
+      <c r="H16" t="n">
+        <v>79</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>63</v>
+      </c>
+      <c r="K16" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STU016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Wateen Noor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>student16@example.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>+966500000016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>111</v>
+      </c>
+      <c r="G17" t="n">
+        <v>90</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>70</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
